--- a/output/yearly_total_coral_cover_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_76_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252412046588737</v>
+        <v>1.252510221359162</v>
       </c>
       <c r="C3" t="n">
-        <v>4.707192480846272</v>
+        <v>4.623675203645997</v>
       </c>
       <c r="D3" t="n">
-        <v>6.118246878062241</v>
+        <v>6.065733193362078</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07785140549725</v>
+        <v>11.94191861836724</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.378505387188774</v>
+        <v>1.370959417793676</v>
       </c>
       <c r="C4" t="n">
-        <v>5.344229161269108</v>
+        <v>5.119688027277109</v>
       </c>
       <c r="D4" t="n">
-        <v>6.396983039686751</v>
+        <v>6.34899795371548</v>
       </c>
       <c r="E4" t="n">
-        <v>13.11971758814463</v>
+        <v>12.83964539878626</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.546823713025913</v>
+        <v>1.533482985317923</v>
       </c>
       <c r="C5" t="n">
-        <v>6.191142315352847</v>
+        <v>5.769494703250065</v>
       </c>
       <c r="D5" t="n">
-        <v>6.710075911723156</v>
+        <v>6.630217710802279</v>
       </c>
       <c r="E5" t="n">
-        <v>14.44804194010192</v>
+        <v>13.93319539937027</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.738254302263144</v>
+        <v>1.719336112787847</v>
       </c>
       <c r="C6" t="n">
-        <v>7.249404043939797</v>
+        <v>6.581790193807334</v>
       </c>
       <c r="D6" t="n">
-        <v>7.015758398369492</v>
+        <v>6.925203552864728</v>
       </c>
       <c r="E6" t="n">
-        <v>16.00341674457243</v>
+        <v>15.22632985945991</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.943294402402642</v>
+        <v>1.942481952745414</v>
       </c>
       <c r="C7" t="n">
-        <v>8.470047751660971</v>
+        <v>7.564267145643813</v>
       </c>
       <c r="D7" t="n">
-        <v>7.530323443884883</v>
+        <v>7.240347569199073</v>
       </c>
       <c r="E7" t="n">
-        <v>17.9436655979485</v>
+        <v>16.7470966675883</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.160398297553134</v>
+        <v>1.207758663021064</v>
       </c>
       <c r="C8" t="n">
-        <v>6.060969169340608</v>
+        <v>5.265316087896116</v>
       </c>
       <c r="D8" t="n">
-        <v>5.768216912067905</v>
+        <v>5.548152915844696</v>
       </c>
       <c r="E8" t="n">
-        <v>12.98958437896165</v>
+        <v>12.02122766676188</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.427727294554242</v>
+        <v>1.546876442458162</v>
       </c>
       <c r="C9" t="n">
-        <v>7.495259573227983</v>
+        <v>6.461101146752227</v>
       </c>
       <c r="D9" t="n">
-        <v>6.319122977417965</v>
+        <v>6.008111607371203</v>
       </c>
       <c r="E9" t="n">
-        <v>15.24210984520019</v>
+        <v>14.01608919658159</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.696401977230046</v>
+        <v>1.905127841189051</v>
       </c>
       <c r="C10" t="n">
-        <v>9.054766804019147</v>
+        <v>7.798188035357534</v>
       </c>
       <c r="D10" t="n">
-        <v>6.848343842354413</v>
+        <v>6.527942161038261</v>
       </c>
       <c r="E10" t="n">
-        <v>17.59951262360361</v>
+        <v>16.23125803758485</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.95727569573007</v>
+        <v>2.265795664168994</v>
       </c>
       <c r="C11" t="n">
-        <v>10.72909441551479</v>
+        <v>9.299233312262039</v>
       </c>
       <c r="D11" t="n">
-        <v>7.33729238491076</v>
+        <v>7.004277106986264</v>
       </c>
       <c r="E11" t="n">
-        <v>20.02366249615562</v>
+        <v>18.5693060834173</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.208391585038729</v>
+        <v>2.625445405713115</v>
       </c>
       <c r="C12" t="n">
-        <v>12.47520283509005</v>
+        <v>10.93957294042472</v>
       </c>
       <c r="D12" t="n">
-        <v>7.898180255990138</v>
+        <v>7.52306237736582</v>
       </c>
       <c r="E12" t="n">
-        <v>22.58177467611891</v>
+        <v>21.08808072350366</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.452500664505385</v>
+        <v>2.979048622975499</v>
       </c>
       <c r="C13" t="n">
-        <v>14.24864108060507</v>
+        <v>12.67097596681837</v>
       </c>
       <c r="D13" t="n">
-        <v>8.331516803562991</v>
+        <v>8.105802878814073</v>
       </c>
       <c r="E13" t="n">
-        <v>25.03265854867345</v>
+        <v>23.75582746860794</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.416121975990811</v>
+        <v>1.699523085775738</v>
       </c>
       <c r="C14" t="n">
-        <v>9.994132724370274</v>
+        <v>8.993044590349802</v>
       </c>
       <c r="D14" t="n">
-        <v>6.330525181478367</v>
+        <v>6.179149502960552</v>
       </c>
       <c r="E14" t="n">
-        <v>17.74077988183945</v>
+        <v>16.87171717908609</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433489092878938</v>
+        <v>1.753087240519444</v>
       </c>
       <c r="C15" t="n">
-        <v>10.77172599351896</v>
+        <v>9.852270181106611</v>
       </c>
       <c r="D15" t="n">
-        <v>6.352408337806029</v>
+        <v>6.236267584393631</v>
       </c>
       <c r="E15" t="n">
-        <v>18.55762342420393</v>
+        <v>17.84162500601969</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653017697025567</v>
+        <v>2.033395845035994</v>
       </c>
       <c r="C16" t="n">
-        <v>12.69839604562628</v>
+        <v>11.80023434091905</v>
       </c>
       <c r="D16" t="n">
-        <v>6.811503016742965</v>
+        <v>6.726493483032233</v>
       </c>
       <c r="E16" t="n">
-        <v>21.16291675939481</v>
+        <v>20.56012366898727</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.321864378906076</v>
+        <v>1.634089601287688</v>
       </c>
       <c r="C17" t="n">
-        <v>11.59785686916561</v>
+        <v>11.02169859397428</v>
       </c>
       <c r="D17" t="n">
-        <v>6.297646450863142</v>
+        <v>6.267909312901506</v>
       </c>
       <c r="E17" t="n">
-        <v>19.21736769893483</v>
+        <v>18.92369750816348</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.501671470938879</v>
+        <v>1.855679875613236</v>
       </c>
       <c r="C18" t="n">
-        <v>13.50175037453441</v>
+        <v>12.97042851699603</v>
       </c>
       <c r="D18" t="n">
-        <v>6.736576031954848</v>
+        <v>6.667578803300383</v>
       </c>
       <c r="E18" t="n">
-        <v>21.73999787742813</v>
+        <v>21.49368719590965</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.498677140440926</v>
+        <v>1.850015191359732</v>
       </c>
       <c r="C19" t="n">
-        <v>14.38142576997068</v>
+        <v>13.96905246427885</v>
       </c>
       <c r="D19" t="n">
-        <v>6.821006334520074</v>
+        <v>6.752382169993223</v>
       </c>
       <c r="E19" t="n">
-        <v>22.70110924493168</v>
+        <v>22.5714498256318</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.663218055672691</v>
+        <v>2.050900406602715</v>
       </c>
       <c r="C20" t="n">
-        <v>16.42938093346065</v>
+        <v>16.04030450079059</v>
       </c>
       <c r="D20" t="n">
-        <v>7.261280909966599</v>
+        <v>7.188464682742612</v>
       </c>
       <c r="E20" t="n">
-        <v>25.35387989909994</v>
+        <v>25.27966959013592</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9899060276691014</v>
+        <v>1.212487867175938</v>
       </c>
       <c r="C21" t="n">
-        <v>12.00681369284666</v>
+        <v>11.77717308734629</v>
       </c>
       <c r="D21" t="n">
-        <v>6.066209247063999</v>
+        <v>6.007176757607639</v>
       </c>
       <c r="E21" t="n">
-        <v>19.06292896757976</v>
+        <v>18.99683771212987</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_76_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.252510221359162</v>
+        <v>1.254876233326397</v>
       </c>
       <c r="C3" t="n">
-        <v>4.623675203645997</v>
+        <v>4.617509828063326</v>
       </c>
       <c r="D3" t="n">
-        <v>6.065733193362078</v>
+        <v>6.04700144716505</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94191861836724</v>
+        <v>11.91938750855477</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370959417793676</v>
+        <v>1.385885858959766</v>
       </c>
       <c r="C4" t="n">
-        <v>5.119688027277109</v>
+        <v>5.086083460728831</v>
       </c>
       <c r="D4" t="n">
-        <v>6.34899795371548</v>
+        <v>6.311584004713874</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83964539878626</v>
+        <v>12.78355332440247</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.533482985317923</v>
+        <v>1.559524257879113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.769494703250065</v>
+        <v>5.651798901576333</v>
       </c>
       <c r="D5" t="n">
-        <v>6.630217710802279</v>
+        <v>6.624723111220941</v>
       </c>
       <c r="E5" t="n">
-        <v>13.93319539937027</v>
+        <v>13.83604627067639</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.719336112787847</v>
+        <v>1.7598785579433</v>
       </c>
       <c r="C6" t="n">
-        <v>6.581790193807334</v>
+        <v>6.378588832244594</v>
       </c>
       <c r="D6" t="n">
-        <v>6.925203552864728</v>
+        <v>6.969952456210723</v>
       </c>
       <c r="E6" t="n">
-        <v>15.22632985945991</v>
+        <v>15.10841984639862</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.942481952745414</v>
+        <v>1.986958332205341</v>
       </c>
       <c r="C7" t="n">
-        <v>7.564267145643813</v>
+        <v>7.302850065865509</v>
       </c>
       <c r="D7" t="n">
-        <v>7.240347569199073</v>
+        <v>7.40091643349162</v>
       </c>
       <c r="E7" t="n">
-        <v>16.7470966675883</v>
+        <v>16.69072483156247</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.207758663021064</v>
+        <v>1.210251225377111</v>
       </c>
       <c r="C8" t="n">
-        <v>5.265316087896116</v>
+        <v>5.06288066082266</v>
       </c>
       <c r="D8" t="n">
-        <v>5.548152915844696</v>
+        <v>5.695505075534806</v>
       </c>
       <c r="E8" t="n">
-        <v>12.02122766676188</v>
+        <v>11.96863696173458</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.546876442458162</v>
+        <v>1.505156560599983</v>
       </c>
       <c r="C9" t="n">
-        <v>6.461101146752227</v>
+        <v>6.320061015422275</v>
       </c>
       <c r="D9" t="n">
-        <v>6.008111607371203</v>
+        <v>6.215584514281561</v>
       </c>
       <c r="E9" t="n">
-        <v>14.01608919658159</v>
+        <v>14.04080209030382</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.905127841189051</v>
+        <v>1.811707687627153</v>
       </c>
       <c r="C10" t="n">
-        <v>7.798188035357534</v>
+        <v>7.76219276875316</v>
       </c>
       <c r="D10" t="n">
-        <v>6.527942161038261</v>
+        <v>6.724706993897636</v>
       </c>
       <c r="E10" t="n">
-        <v>16.23125803758485</v>
+        <v>16.29860745027795</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.265795664168994</v>
+        <v>2.113210458368608</v>
       </c>
       <c r="C11" t="n">
-        <v>9.299233312262039</v>
+        <v>9.32204208381582</v>
       </c>
       <c r="D11" t="n">
-        <v>7.004277106986264</v>
+        <v>7.2501965461698</v>
       </c>
       <c r="E11" t="n">
-        <v>18.5693060834173</v>
+        <v>18.68544908835423</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.625445405713115</v>
+        <v>2.412474086376556</v>
       </c>
       <c r="C12" t="n">
-        <v>10.93957294042472</v>
+        <v>11.00830464657021</v>
       </c>
       <c r="D12" t="n">
-        <v>7.52306237736582</v>
+        <v>7.720093245551763</v>
       </c>
       <c r="E12" t="n">
-        <v>21.08808072350366</v>
+        <v>21.14087197849853</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.979048622975499</v>
+        <v>2.699354053149367</v>
       </c>
       <c r="C13" t="n">
-        <v>12.67097596681837</v>
+        <v>12.71654127887844</v>
       </c>
       <c r="D13" t="n">
-        <v>8.105802878814073</v>
+        <v>8.289047309670041</v>
       </c>
       <c r="E13" t="n">
-        <v>23.75582746860794</v>
+        <v>23.70494264169785</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.699523085775738</v>
+        <v>1.564788030844906</v>
       </c>
       <c r="C14" t="n">
-        <v>8.993044590349802</v>
+        <v>8.83841932693093</v>
       </c>
       <c r="D14" t="n">
-        <v>6.179149502960552</v>
+        <v>6.294907374768294</v>
       </c>
       <c r="E14" t="n">
-        <v>16.87171717908609</v>
+        <v>16.69811473254413</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.753087240519444</v>
+        <v>1.581212669936955</v>
       </c>
       <c r="C15" t="n">
-        <v>9.852270181106611</v>
+        <v>9.654457836177922</v>
       </c>
       <c r="D15" t="n">
-        <v>6.236267584393631</v>
+        <v>6.330957150468237</v>
       </c>
       <c r="E15" t="n">
-        <v>17.84162500601969</v>
+        <v>17.56662765658312</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.033395845035994</v>
+        <v>1.811353966766493</v>
       </c>
       <c r="C16" t="n">
-        <v>11.80023434091905</v>
+        <v>11.42474529647577</v>
       </c>
       <c r="D16" t="n">
-        <v>6.726493483032233</v>
+        <v>6.780087090207068</v>
       </c>
       <c r="E16" t="n">
-        <v>20.56012366898727</v>
+        <v>20.01618635344933</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.634089601287688</v>
+        <v>1.434156681317825</v>
       </c>
       <c r="C17" t="n">
-        <v>11.02169859397428</v>
+        <v>10.56375255985132</v>
       </c>
       <c r="D17" t="n">
-        <v>6.267909312901506</v>
+        <v>6.296605798296642</v>
       </c>
       <c r="E17" t="n">
-        <v>18.92369750816348</v>
+        <v>18.29451503946579</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.855679875613236</v>
+        <v>1.627443169329938</v>
       </c>
       <c r="C18" t="n">
-        <v>12.97042851699603</v>
+        <v>12.28632708172277</v>
       </c>
       <c r="D18" t="n">
-        <v>6.667578803300383</v>
+        <v>6.696599265437918</v>
       </c>
       <c r="E18" t="n">
-        <v>21.49368719590965</v>
+        <v>20.61036951649062</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.850015191359732</v>
+        <v>1.626127627406247</v>
       </c>
       <c r="C19" t="n">
-        <v>13.96905246427885</v>
+        <v>13.09559153181046</v>
       </c>
       <c r="D19" t="n">
-        <v>6.752382169993223</v>
+        <v>6.775276526456258</v>
       </c>
       <c r="E19" t="n">
-        <v>22.5714498256318</v>
+        <v>21.49699568567296</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.050900406602715</v>
+        <v>1.815035520657418</v>
       </c>
       <c r="C20" t="n">
-        <v>16.04030450079059</v>
+        <v>14.99281897026742</v>
       </c>
       <c r="D20" t="n">
-        <v>7.188464682742612</v>
+        <v>7.195690345845869</v>
       </c>
       <c r="E20" t="n">
-        <v>25.27966959013592</v>
+        <v>24.00354483677071</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.212487867175938</v>
+        <v>1.084340339340602</v>
       </c>
       <c r="C21" t="n">
-        <v>11.77717308734629</v>
+        <v>10.89586799072097</v>
       </c>
       <c r="D21" t="n">
-        <v>6.007176757607639</v>
+        <v>5.999479855606344</v>
       </c>
       <c r="E21" t="n">
-        <v>18.99683771212987</v>
+        <v>17.97968818566792</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_76_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254876233326397</v>
+        <v>2.639850376263905</v>
       </c>
       <c r="C3" t="n">
-        <v>4.617509828063326</v>
+        <v>7.718566342484226</v>
       </c>
       <c r="D3" t="n">
-        <v>6.04700144716505</v>
+        <v>8.233042045118641</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91938750855477</v>
+        <v>18.59145876386677</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385885858959766</v>
+        <v>1.180590639802331</v>
       </c>
       <c r="C4" t="n">
-        <v>5.086083460728831</v>
+        <v>4.519433722686927</v>
       </c>
       <c r="D4" t="n">
-        <v>6.311584004713874</v>
+        <v>5.832454447886855</v>
       </c>
       <c r="E4" t="n">
-        <v>12.78355332440247</v>
+        <v>11.53247881037611</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.559524257879113</v>
+        <v>1.367821891615017</v>
       </c>
       <c r="C5" t="n">
-        <v>5.651798901576333</v>
+        <v>5.196955294101335</v>
       </c>
       <c r="D5" t="n">
-        <v>6.624723111220941</v>
+        <v>6.135449248995178</v>
       </c>
       <c r="E5" t="n">
-        <v>13.83604627067639</v>
+        <v>12.70022643471153</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.7598785579433</v>
+        <v>1.569285663224588</v>
       </c>
       <c r="C6" t="n">
-        <v>6.378588832244594</v>
+        <v>6.109222481596618</v>
       </c>
       <c r="D6" t="n">
-        <v>6.969952456210723</v>
+        <v>6.478599119866606</v>
       </c>
       <c r="E6" t="n">
-        <v>15.10841984639862</v>
+        <v>14.15710726468781</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.986958332205341</v>
+        <v>1.785243102673835</v>
       </c>
       <c r="C7" t="n">
-        <v>7.302850065865509</v>
+        <v>7.19826610953342</v>
       </c>
       <c r="D7" t="n">
-        <v>7.40091643349162</v>
+        <v>6.794792883813006</v>
       </c>
       <c r="E7" t="n">
-        <v>16.69072483156247</v>
+        <v>15.77830209602026</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.210251225377111</v>
+        <v>2.005052823184887</v>
       </c>
       <c r="C8" t="n">
-        <v>5.06288066082266</v>
+        <v>8.466282195995245</v>
       </c>
       <c r="D8" t="n">
-        <v>5.695505075534806</v>
+        <v>7.169732945138207</v>
       </c>
       <c r="E8" t="n">
-        <v>11.96863696173458</v>
+        <v>17.64106796431834</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.505156560599983</v>
+        <v>2.204282767814621</v>
       </c>
       <c r="C9" t="n">
-        <v>6.320061015422275</v>
+        <v>9.844598343110809</v>
       </c>
       <c r="D9" t="n">
-        <v>6.215584514281561</v>
+        <v>7.614950805148514</v>
       </c>
       <c r="E9" t="n">
-        <v>14.04080209030382</v>
+        <v>19.66383191607395</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.811707687627153</v>
+        <v>1.319920518451667</v>
       </c>
       <c r="C10" t="n">
-        <v>7.76219276875316</v>
+        <v>7.185990678527911</v>
       </c>
       <c r="D10" t="n">
-        <v>6.724706993897636</v>
+        <v>5.972462158785471</v>
       </c>
       <c r="E10" t="n">
-        <v>16.29860745027795</v>
+        <v>14.47837335576505</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.113210458368608</v>
+        <v>1.280071379136289</v>
       </c>
       <c r="C11" t="n">
-        <v>9.32204208381582</v>
+        <v>7.742386372432748</v>
       </c>
       <c r="D11" t="n">
-        <v>7.2501965461698</v>
+        <v>5.821999505632605</v>
       </c>
       <c r="E11" t="n">
-        <v>18.68544908835423</v>
+        <v>14.84445725720164</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.412474086376556</v>
+        <v>1.415405300166712</v>
       </c>
       <c r="C12" t="n">
-        <v>11.00830464657021</v>
+        <v>9.2068790578118</v>
       </c>
       <c r="D12" t="n">
-        <v>7.720093245551763</v>
+        <v>6.244553535017475</v>
       </c>
       <c r="E12" t="n">
-        <v>21.14087197849853</v>
+        <v>16.86683789299599</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.699354053149367</v>
+        <v>1.130688648458094</v>
       </c>
       <c r="C13" t="n">
-        <v>12.71654127887844</v>
+        <v>8.778935233530616</v>
       </c>
       <c r="D13" t="n">
-        <v>8.289047309670041</v>
+        <v>5.705328608459914</v>
       </c>
       <c r="E13" t="n">
-        <v>23.70494264169785</v>
+        <v>15.61495249044862</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.564788030844906</v>
+        <v>1.24829220594982</v>
       </c>
       <c r="C14" t="n">
-        <v>8.83841932693093</v>
+        <v>10.30822326738996</v>
       </c>
       <c r="D14" t="n">
-        <v>6.294907374768294</v>
+        <v>6.044306455782253</v>
       </c>
       <c r="E14" t="n">
-        <v>16.69811473254413</v>
+        <v>17.60082192912203</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.581212669936955</v>
+        <v>1.22665448654822</v>
       </c>
       <c r="C15" t="n">
-        <v>9.654457836177922</v>
+        <v>11.14790226135521</v>
       </c>
       <c r="D15" t="n">
-        <v>6.330957150468237</v>
+        <v>6.088161125730958</v>
       </c>
       <c r="E15" t="n">
-        <v>17.56662765658312</v>
+        <v>18.46271787363439</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.811353966766493</v>
+        <v>1.356107738830204</v>
       </c>
       <c r="C16" t="n">
-        <v>11.42474529647577</v>
+        <v>12.99414754153064</v>
       </c>
       <c r="D16" t="n">
-        <v>6.780087090207068</v>
+        <v>6.47301604327275</v>
       </c>
       <c r="E16" t="n">
-        <v>20.01618635344933</v>
+        <v>20.82327132363359</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.434156681317825</v>
+        <v>0.8104425473327845</v>
       </c>
       <c r="C17" t="n">
-        <v>10.56375255985132</v>
+        <v>9.692942346184397</v>
       </c>
       <c r="D17" t="n">
-        <v>6.296605798296642</v>
+        <v>5.371907453143613</v>
       </c>
       <c r="E17" t="n">
-        <v>18.29451503946579</v>
+        <v>15.87529234666079</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.627443169329938</v>
+        <v>0.6610401817005047</v>
       </c>
       <c r="C18" t="n">
-        <v>12.28632708172277</v>
+        <v>8.656373850132443</v>
       </c>
       <c r="D18" t="n">
-        <v>6.696599265437918</v>
+        <v>4.890576188705487</v>
       </c>
       <c r="E18" t="n">
-        <v>20.61036951649062</v>
+        <v>14.20799022053843</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.626127627406247</v>
+        <v>0.7797727490521141</v>
       </c>
       <c r="C19" t="n">
-        <v>13.09559153181046</v>
+        <v>10.69048637099254</v>
       </c>
       <c r="D19" t="n">
-        <v>6.775276526456258</v>
+        <v>5.397648877948964</v>
       </c>
       <c r="E19" t="n">
-        <v>21.49699568567296</v>
+        <v>16.86790799799362</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.815035520657418</v>
+        <v>0.89033717550439</v>
       </c>
       <c r="C20" t="n">
-        <v>14.99281897026742</v>
+        <v>12.83905103921373</v>
       </c>
       <c r="D20" t="n">
-        <v>7.195690345845869</v>
+        <v>5.875858184687584</v>
       </c>
       <c r="E20" t="n">
-        <v>24.00354483677071</v>
+        <v>19.6052463994057</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.084340339340602</v>
+        <v>0.991113577345325</v>
       </c>
       <c r="C21" t="n">
-        <v>10.89586799072097</v>
+        <v>15.07884952159057</v>
       </c>
       <c r="D21" t="n">
-        <v>5.999479855606344</v>
+        <v>6.306010941303325</v>
       </c>
       <c r="E21" t="n">
-        <v>17.97968818566792</v>
+        <v>22.37597404023922</v>
       </c>
     </row>
   </sheetData>
